--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484835_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484835_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7565</v>
+        <v>1.4936</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6415999999999999</v>
+        <v>1.2463</v>
       </c>
       <c r="F2" t="n">
-        <v>0.115</v>
+        <v>0.2472</v>
       </c>
       <c r="G2" t="n">
         <v>1.7498</v>
@@ -610,13 +610,13 @@
         <v>0.9435</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6348</v>
+        <v>-0.8978</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2933</v>
+        <v>-0.6886</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3415</v>
+        <v>-0.2092</v>
       </c>
       <c r="V2" t="n">
         <v>0.6415999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7074</v>
+        <v>0.7338</v>
       </c>
       <c r="E3" t="n">
         <v>0.6762</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0312</v>
+        <v>0.0577</v>
       </c>
       <c r="G3" t="n">
         <v>0.2536</v>
@@ -688,13 +688,13 @@
         <v>0.5661</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1123</v>
+        <v>-0.0858</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MANDU</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0735</v>
+        <v>0.6048</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0423</v>
+        <v>2.6887</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0312</v>
+        <v>-2.0839</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3803</v>
+        <v>3.1053</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3803</v>
+        <v>-0.9485</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>4.0538</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0423</v>
+        <v>5.7346</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0423</v>
+        <v>1.1833</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>4.5513</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4226</v>
+        <v>-2.6293</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4226</v>
+        <v>-2.1318</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.4976</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5661</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5661</v>
+        <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1123</v>
+        <v>-1.0741</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-1.1589</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1123</v>
+        <v>0.0847</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.0489</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0489</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>A. MANDU</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1322</v>
+        <v>0.0999</v>
       </c>
       <c r="E6" t="n">
-        <v>2.084</v>
+        <v>0.0423</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2162</v>
+        <v>0.0577</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1053</v>
+        <v>-0.3803</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9485</v>
+        <v>-0.3803</v>
       </c>
       <c r="I6" t="n">
-        <v>4.0538</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7346</v>
+        <v>0.0423</v>
       </c>
       <c r="K6" t="n">
-        <v>1.1833</v>
+        <v>0.0423</v>
       </c>
       <c r="L6" t="n">
-        <v>4.5513</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.6293</v>
+        <v>-0.4226</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1318</v>
+        <v>-0.4226</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4976</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3774</v>
+        <v>0.5661</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5096</v>
+        <v>0.5661</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.8112</v>
+        <v>-0.0858</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.7636</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0475</v>
+        <v>-0.0858</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0489</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>R. AMOROS PEREZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6485</v>
+        <v>-1.1453</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7662</v>
+        <v>0.0423</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1177</v>
+        <v>-1.1875</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3517</v>
+        <v>-0.3803</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2067</v>
+        <v>-0.3803</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.145</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9001</v>
+        <v>0.0423</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5384</v>
+        <v>0.0423</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3617</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4516</v>
+        <v>-0.4226</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6683</v>
+        <v>-0.4226</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2167</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9435</v>
+        <v>0.5661</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8277</v>
+        <v>-0.0858</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.3539</v>
+        <v>-0.0858</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1245</v>
+        <v>-1.2452</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.7281</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. AMOROS PEREZ</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1717</v>
+        <v>-1.5434</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0423</v>
+        <v>-1.9997</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.214</v>
+        <v>0.4563</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.3803</v>
+        <v>-1.3517</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3803</v>
+        <v>-1.2067</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.145</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0423</v>
+        <v>-0.9001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0423</v>
+        <v>-0.5384</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-0.3617</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4226</v>
+        <v>-0.4516</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4226</v>
+        <v>-0.6683</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.2167</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5661</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5661</v>
+        <v>0.9435</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1123</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.7597</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1123</v>
+        <v>0.6926</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2452</v>
+        <v>-0.1245</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2452</v>
+        <v>-0.7281</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0669</v>
+        <v>-1.5571</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0864</v>
+        <v>0.4374</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1532</v>
+        <v>-1.9945</v>
       </c>
       <c r="G9" t="n">
         <v>1.331</v>
@@ -1156,13 +1156,13 @@
         <v>2.2644</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1709</v>
+        <v>-1.6611</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.5873</v>
+        <v>-1.2362</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5837</v>
+        <v>-0.4249</v>
       </c>
       <c r="V9" t="n">
         <v>2.1696</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1604</v>
+        <v>-2.1726</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6371</v>
+        <v>1.5984</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.7975</v>
+        <v>-3.771</v>
       </c>
       <c r="G10" t="n">
         <v>-0.6272</v>
@@ -1234,13 +1234,13 @@
         <v>1.6983</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2763</v>
+        <v>-0.2885</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.291</v>
+        <v>-0.3297</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0147</v>
+        <v>0.0412</v>
       </c>
       <c r="V10" t="n">
         <v>0.8189</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9122</v>
+        <v>-3.2251</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9903</v>
+        <v>0.7568</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.9026</v>
+        <v>-3.9819</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1461</v>
@@ -1312,13 +1312,13 @@
         <v>0.3774</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2904</v>
+        <v>-0.0225</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1793</v>
+        <v>-0.0543</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1111</v>
+        <v>0.0318</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4904</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. ALBERT ABELLAN</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8395</v>
+        <v>-4.6977</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.7481</v>
+        <v>-2.3865</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0914</v>
+        <v>-2.3112</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.8913</v>
+        <v>-0.2682</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.2867</v>
+        <v>-0.8655</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6046</v>
+        <v>0.5974</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.4577</v>
+        <v>0.8756</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4805</v>
+        <v>0.1268</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9771</v>
+        <v>0.7489</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4337</v>
+        <v>-1.1438</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8062</v>
+        <v>-0.9923</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6274999999999999</v>
+        <v>-0.1515</v>
       </c>
       <c r="P12" t="n">
-        <v>0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7295</v>
+        <v>-0.3805</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3469</v>
+        <v>-0.4317</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3826</v>
+        <v>0.0512</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.4074</v>
+        <v>-1.9733</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.4074</v>
+        <v>-1.9733</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>F. ALBERT ABELLAN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.848</v>
+        <v>-5.2453</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.4839</v>
+        <v>-3.3125</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.3641</v>
+        <v>-1.9327</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2682</v>
+        <v>-3.8913</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8655</v>
+        <v>-2.2867</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5974</v>
+        <v>-1.6046</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8756</v>
+        <v>-1.4577</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1268</v>
+        <v>-0.4805</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7489</v>
+        <v>-0.9771</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.1438</v>
+        <v>-2.4337</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9923</v>
+        <v>-1.8062</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1515</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.0757</v>
+        <v>0.1887</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5308</v>
+        <v>-1.1353</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5291</v>
+        <v>-0.9114</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0017</v>
+        <v>-0.2239</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.9733</v>
+        <v>-0.4074</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.9733</v>
+        <v>-0.4074</v>
       </c>
     </row>
     <row r="14">
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.625</v>
+        <v>-16.0374</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.181</v>
+        <v>0.4066999999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.4439</v>
+        <v>-16.4438</v>
       </c>
       <c r="G14" t="n">
-        <v>0.01159999999999983</v>
+        <v>0.01159999999999961</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.589200000000001</v>
+        <v>-6.5892</v>
       </c>
       <c r="I14" t="n">
         <v>6.600800000000001</v>
@@ -1537,7 +1537,7 @@
         <v>-3.8948</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.6045</v>
+        <v>-6.604499999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-17.9265</v>
@@ -1546,13 +1546,13 @@
         <v>11.322</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.3723</v>
+        <v>-5.7843</v>
       </c>
       <c r="T14" t="n">
-        <v>-6.1581</v>
+        <v>-5.570499999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2142</v>
+        <v>-0.2139</v>
       </c>
       <c r="V14" t="n">
         <v>-3.6596</v>
@@ -1561,7 +1561,7 @@
         <v>6.169</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.8286</v>
+        <v>-9.828600000000002</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.8328</v>
+        <v>7.2406</v>
       </c>
       <c r="E15" t="n">
-        <v>6.1175</v>
+        <v>6.6047</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7153</v>
+        <v>0.6359</v>
       </c>
       <c r="G15" t="n">
         <v>2.1836</v>
@@ -1624,13 +1624,13 @@
         <v>2.0757</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4421</v>
+        <v>0.8499</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2199</v>
+        <v>0.2673</v>
       </c>
       <c r="U15" t="n">
-        <v>0.662</v>
+        <v>0.5826</v>
       </c>
       <c r="V15" t="n">
         <v>4.0184</v>
@@ -1657,10 +1657,10 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3419</v>
+        <v>4.9522</v>
       </c>
       <c r="E16" t="n">
-        <v>4.8518</v>
+        <v>4.462</v>
       </c>
       <c r="F16" t="n">
         <v>0.4902</v>
@@ -1702,10 +1702,10 @@
         <v>2.2644</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9558</v>
+        <v>0.5661</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3121</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U16" t="n">
         <v>0.6438</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3193</v>
+        <v>4.4806</v>
       </c>
       <c r="E17" t="n">
-        <v>3.8439</v>
+        <v>4.4285</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4754</v>
+        <v>0.0521</v>
       </c>
       <c r="G17" t="n">
         <v>0.5241</v>
@@ -1780,13 +1780,13 @@
         <v>2.6418</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1534</v>
+        <v>1.3147</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5139</v>
+        <v>0.0708</v>
       </c>
       <c r="U17" t="n">
-        <v>1.6672</v>
+        <v>1.244</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3426</v>
+        <v>2.3767</v>
       </c>
       <c r="E18" t="n">
-        <v>3.3321</v>
+        <v>2.2603</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0106</v>
+        <v>0.1164</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2362</v>
@@ -1858,13 +1858,13 @@
         <v>2.2644</v>
       </c>
       <c r="S18" t="n">
-        <v>2.409</v>
+        <v>1.443</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6576</v>
+        <v>0.5859</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7513</v>
+        <v>0.8571</v>
       </c>
       <c r="V18" t="n">
         <v>0.9054</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.3735</v>
+        <v>2.1509</v>
       </c>
       <c r="E19" t="n">
-        <v>3.5706</v>
+        <v>3.0834</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1971</v>
+        <v>-0.9325</v>
       </c>
       <c r="G19" t="n">
         <v>0.2115</v>
@@ -1936,13 +1936,13 @@
         <v>1.887</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2186</v>
+        <v>0.9959</v>
       </c>
       <c r="T19" t="n">
-        <v>1.0081</v>
+        <v>0.5209</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2105</v>
+        <v>0.475</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>H. RODRÍGUEZ GUTIERREZ</t>
+          <t>L. CARRION GALINDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.317</v>
+        <v>0.333</v>
       </c>
       <c r="E21" t="n">
-        <v>0.317</v>
+        <v>-0.8286</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1.1616</v>
       </c>
       <c r="G21" t="n">
-        <v>0.317</v>
+        <v>0.8414</v>
       </c>
       <c r="H21" t="n">
-        <v>0.317</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>1.8228</v>
       </c>
       <c r="J21" t="n">
-        <v>0.317</v>
+        <v>1.4974</v>
       </c>
       <c r="K21" t="n">
-        <v>0.317</v>
+        <v>-0.4117</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.909</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>-0.656</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.5697</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-0.0863</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.774</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.4531</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.2088</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.4008</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.6097</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.8488</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. CARRION GALINDO</t>
+          <t>H. RODRÍGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0407</v>
+        <v>0.317</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1209</v>
+        <v>0.317</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1616</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8414</v>
+        <v>0.317</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9814000000000001</v>
+        <v>0.317</v>
       </c>
       <c r="I22" t="n">
-        <v>1.8228</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4974</v>
+        <v>0.317</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4117</v>
+        <v>0.317</v>
       </c>
       <c r="L22" t="n">
-        <v>1.909</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.656</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5697</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0863</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.774</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4531</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0835</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6931</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6097</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8488</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.0495</v>
+        <v>0.0827</v>
       </c>
       <c r="E23" t="n">
         <v>-1.0652</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0157</v>
+        <v>1.148</v>
       </c>
       <c r="G23" t="n">
         <v>1.7493</v>
@@ -2248,13 +2248,13 @@
         <v>1.1322</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1005</v>
+        <v>0.0318</v>
       </c>
       <c r="T23" t="n">
         <v>-0.3527</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2522</v>
+        <v>0.3845</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2669</v>
+        <v>-0.4076</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8452</v>
+        <v>-0.7477</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5783</v>
+        <v>0.3402</v>
       </c>
       <c r="G24" t="n">
         <v>-1.7527</v>
@@ -2326,13 +2326,13 @@
         <v>0.9435</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2404</v>
+        <v>0.0998</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3527</v>
+        <v>-0.2553</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.3551</v>
       </c>
       <c r="V24" t="n">
         <v>0.3018</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.0175</v>
+        <v>-0.6194</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.7625</v>
+        <v>-0.4702</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.255</v>
+        <v>-0.1492</v>
       </c>
       <c r="G25" t="n">
         <v>-1.1004</v>
@@ -2404,13 +2404,13 @@
         <v>0.1887</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.1058</v>
+        <v>0.2923</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.1764</v>
+        <v>0.1159</v>
       </c>
       <c r="U25" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1764</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.0816</v>
+        <v>-0.6751</v>
       </c>
       <c r="E26" t="n">
-        <v>1.2634</v>
+        <v>1.4583</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.345</v>
+        <v>-2.1334</v>
       </c>
       <c r="G26" t="n">
         <v>0.6328</v>
@@ -2482,13 +2482,13 @@
         <v>1.5096</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4127</v>
+        <v>-0.0062</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5755</v>
+        <v>-0.3807</v>
       </c>
       <c r="U26" t="n">
-        <v>0.1629</v>
+        <v>0.3745</v>
       </c>
       <c r="V26" t="n">
         <v>-1.8678</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-4.161</v>
+        <v>-4.2404</v>
       </c>
       <c r="E27" t="n">
         <v>-3.6924</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.4687</v>
+        <v>-0.548</v>
       </c>
       <c r="G27" t="n">
         <v>-5.3826</v>
@@ -2560,13 +2560,13 @@
         <v>0.5661</v>
       </c>
       <c r="S27" t="n">
-        <v>0.6554</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="T27" t="n">
         <v>0.1205</v>
       </c>
       <c r="U27" t="n">
-        <v>0.535</v>
+        <v>0.4556</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>16.6252</v>
+        <v>16.6251</v>
       </c>
       <c r="E28" t="n">
         <v>16.444</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1812999999999999</v>
+        <v>0.1813000000000002</v>
       </c>
       <c r="G28" t="n">
         <v>-0.01130000000000031</v>
@@ -2638,7 +2638,7 @@
         <v>17.9265</v>
       </c>
       <c r="S28" t="n">
-        <v>6.372199999999999</v>
+        <v>6.3722</v>
       </c>
       <c r="T28" t="n">
         <v>0.2140999999999999</v>
